--- a/branches/feat/english-default-language/all-profiles.xlsx
+++ b/branches/feat/english-default-language/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="350">
   <si>
     <t>Property</t>
   </si>
@@ -48,7 +48,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Beispiel-Patient (Vorlage)</t>
+    <t>Example Patient — template starter</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,10 +60,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T11:41:02+00:00</t>
+    <t>2026-07-26T11:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Minimales Beispielprofil, das nur mit der Vorlage ausgeliefert wird, damit ein neu erstelltes Modul sofort eine gerenderte IG erzeugt. Kein MII-Artefakt — ersetzen Sie es durch die Profile Ihres Moduls.</t>
+    <t>Minimal example profile shipped with the template so that a newly created module renders a complete IG immediately. Not an MII artifact — replace it with your module's profiles.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -117,13 +120,10 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Patient|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1313,98 +1313,100 @@
       <c r="A8" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1580,10 +1582,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
@@ -1663,7 +1665,7 @@
         <v>78</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>76</v>
